--- a/sheets_template/Mobiq.xlsx
+++ b/sheets_template/Mobiq.xlsx
@@ -495,7 +495,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
     </row>
@@ -527,7 +527,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
     </row>
@@ -559,7 +559,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
     </row>
@@ -694,12 +694,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
     </row>
@@ -736,12 +736,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
     </row>
@@ -778,12 +778,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
     </row>
@@ -862,12 +862,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
     </row>
@@ -965,12 +965,12 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -1049,12 +1049,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
     </row>
@@ -1235,7 +1235,7 @@
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1269,7 @@
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
     </row>
@@ -1303,7 +1303,7 @@
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
     </row>
@@ -1507,7 +1507,7 @@
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
     </row>
@@ -1677,7 +1677,7 @@
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
     </row>
@@ -1745,7 +1745,7 @@
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
     </row>
@@ -1813,7 +1813,7 @@
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
     </row>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
@@ -2308,7 +2308,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
@@ -2644,7 +2644,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
     </row>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T04:34:33Z</t>
+          <t>2026-10-23T14:37:27Z</t>
         </is>
       </c>
     </row>

--- a/sheets_template/Mobiq.xlsx
+++ b/sheets_template/Mobiq.xlsx
@@ -11,9 +11,8 @@
     <sheet name="MobileLines" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Bills" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="BillShares" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Payments" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Settings" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="AuditLog" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Settings" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="AuditLog" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,7 +494,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
     </row>
@@ -527,7 +526,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
     </row>
@@ -559,7 +558,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
     </row>
@@ -591,7 +590,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
     </row>
@@ -694,12 +693,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
     </row>
@@ -736,12 +735,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
     </row>
@@ -778,12 +777,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
     </row>
@@ -820,12 +819,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
     </row>
@@ -862,12 +861,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
     </row>
@@ -965,12 +964,12 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -1007,12 +1006,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -1049,12 +1048,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -1091,12 +1090,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -1124,8 +1123,8 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -1157,12 +1156,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>amount_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>payment_status</t>
+          <t>paid_date</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -1197,11 +1196,19 @@
           <t>40.00</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
     </row>
@@ -1231,11 +1238,19 @@
           <t>40.00</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
     </row>
@@ -1265,11 +1280,19 @@
           <t>40.00</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
     </row>
@@ -1299,11 +1322,19 @@
           <t>40.00</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
     </row>
@@ -1333,11 +1364,19 @@
           <t>40.00</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
     </row>
@@ -1367,11 +1406,19 @@
           <t>40.00</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
     </row>
@@ -1401,11 +1448,19 @@
           <t>40.00</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
     </row>
@@ -1435,11 +1490,15 @@
           <t>40.00</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
     </row>
@@ -1469,11 +1528,19 @@
           <t>40.00</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
     </row>
@@ -1503,11 +1570,15 @@
           <t>40.00</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
     </row>
@@ -1537,11 +1608,19 @@
           <t>42.00</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
     </row>
@@ -1571,11 +1650,19 @@
           <t>42.00</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr"/>
-      <c r="G13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
     </row>
@@ -1605,11 +1692,15 @@
           <t>42.00</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
     </row>
@@ -1639,11 +1730,19 @@
           <t>42.00</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
     </row>
@@ -1673,11 +1772,15 @@
           <t>42.00</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
     </row>
@@ -1707,11 +1810,19 @@
           <t>43.00</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
     </row>
@@ -1741,11 +1852,19 @@
           <t>43.00</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
     </row>
@@ -1775,11 +1894,15 @@
           <t>43.00</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
     </row>
@@ -1809,11 +1932,15 @@
           <t>43.00</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
     </row>
@@ -1843,11 +1970,15 @@
           <t>43.00</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
     </row>
@@ -1857,852 +1988,6 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="23" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>payment_id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>share_id</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>user_id</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>payment_date</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>payment_status</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>payment_method</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>reverses_payment_id</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>p_000</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>s_b_m3_l_alex1</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>u_alex</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>SAMPLE transfer</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>SAMPLE data</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T14:37:27Z</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>p_001</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>s_b_m3_l_alex2</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>u_alex</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>SAMPLE transfer</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>SAMPLE data</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T14:37:27Z</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>p_002</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>s_b_m3_l_sam</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>u_sam</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>SAMPLE transfer</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>SAMPLE data</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T14:37:27Z</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>p_003</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>s_b_m3_l_jo</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>u_jo</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>SAMPLE transfer</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>SAMPLE data</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T14:37:27Z</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>p_004</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>s_b_m3_l_admin</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>u_admin</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>SAMPLE transfer</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>SAMPLE data</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T14:37:27Z</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>p_005</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>s_b_m2_l_admin</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>u_admin</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>SAMPLE transfer</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>SAMPLE data</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T14:37:27Z</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>p_006</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>s_b_m2_l_alex1</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>u_alex</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>SAMPLE transfer</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>SAMPLE data</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T14:37:27Z</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>p_007</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>s_b_m2_l_sam</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>u_sam</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>SAMPLE transfer</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>SAMPLE data</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T14:37:27Z</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>p_008</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>s_b_m2_l_jo</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>u_jo</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>20.00</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>SAMPLE transfer</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>SAMPLE data</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T14:37:27Z</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>p_009</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>s_b_m1_l_admin</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>u_admin</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>42.00</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>SAMPLE transfer</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>SAMPLE data</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T14:37:27Z</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>p_010</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>s_b_m1_l_alex1</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>u_alex</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>42.00</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>SAMPLE transfer</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>SAMPLE data</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T14:37:27Z</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>p_011</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>s_b_m1_l_alex2</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>u_alex</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>20.00</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>SAMPLE transfer</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>SAMPLE data</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T14:37:27Z</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>p_012</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>s_b_m1_l_sam</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>u_sam</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>42.00</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>SAMPLE transfer</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>SAMPLE data</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T14:37:27Z</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>p_013</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>s_b_m0_l_admin</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>u_admin</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>43.00</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>SAMPLE transfer</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>SAMPLE data</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T14:37:27Z</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>p_014</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>s_b_m0_l_alex1</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>u_alex</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>43.00</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>SAMPLE transfer</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>SAMPLE data</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T14:37:27Z</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>p_015</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>s_b_m0_l_sam</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>u_sam</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>20.00</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>SAMPLE transfer</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>SAMPLE data</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T14:37:27Z</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2746,7 +2031,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2048,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2065,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2082,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
     </row>
@@ -2814,7 +2099,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2116,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2133,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2150,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T14:37:27Z</t>
+          <t>2026-10-23T14:58:29Z</t>
         </is>
       </c>
     </row>
@@ -2874,7 +2159,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
